--- a/tests/TC-19/results/teacher_timetables_even.xlsx
+++ b/tests/TC-19/results/teacher_timetables_even.xlsx
@@ -58,14 +58,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFDAB3"/>
-        <bgColor rgb="00FFDAB3"/>
+        <fgColor rgb="00BBDEFB"/>
+        <bgColor rgb="00BBDEFB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00BBDEFB"/>
-        <bgColor rgb="00BBDEFB"/>
+        <fgColor rgb="00FFDAB3"/>
+        <bgColor rgb="00FFDAB3"/>
       </patternFill>
     </fill>
   </fills>
@@ -620,34 +620,10 @@
       </c>
       <c r="B3" s="3" t="inlineStr"/>
       <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>CS201 LEC
-(CSE_2_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>CS201 LEC
-(CSE_2_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>CS201 LEC
-(CSE_2_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>CS201 LEC
-(CSE_2_B)
-Room: 101</t>
-        </is>
-      </c>
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="3" t="inlineStr"/>
       <c r="I3" s="3" t="inlineStr"/>
       <c r="J3" s="3" t="inlineStr"/>
@@ -660,7 +636,13 @@
       <c r="Q3" s="3" t="inlineStr"/>
       <c r="R3" s="3" t="inlineStr"/>
       <c r="S3" s="3" t="inlineStr"/>
-      <c r="T3" s="3" t="inlineStr"/>
+      <c r="T3" s="4" t="inlineStr">
+        <is>
+          <t>CS201 TUT
+(CSE_2_B)
+Room: 101</t>
+        </is>
+      </c>
       <c r="U3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="35" customHeight="1">
@@ -670,23 +652,35 @@
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr"/>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr"/>
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>CS201 LEC
 (CSE_2_B)
 Room: 101</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>CS201 LEC
 (CSE_2_B)
 Room: 101</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>CS201 LEC
+(CSE_2_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>CS201 LEC
+(CSE_2_B)
+Room: 101</t>
+        </is>
+      </c>
       <c r="H4" s="5" t="inlineStr"/>
       <c r="I4" s="5" t="inlineStr"/>
       <c r="J4" s="5" t="inlineStr"/>
@@ -719,10 +713,16 @@
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="3" t="inlineStr"/>
+      <c r="M5" s="6" t="inlineStr">
+        <is>
+          <t>CS201 LEC
+(CSE_2_B)
+Room: 101</t>
+        </is>
+      </c>
       <c r="N5" s="6" t="inlineStr">
         <is>
-          <t>CS201 TUT
+          <t>CS201 LEC
 (CSE_2_B)
 Room: 101</t>
         </is>
@@ -953,10 +953,34 @@
       <c r="C3" s="3" t="inlineStr"/>
       <c r="D3" s="3" t="inlineStr"/>
       <c r="E3" s="3" t="inlineStr"/>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>CS202 LEC
+(CSE_2_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>CS202 LEC
+(CSE_2_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>CS202 LEC
+(CSE_2_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>CS202 LEC
+(CSE_2_B)
+Room: 101</t>
+        </is>
+      </c>
       <c r="J3" s="3" t="inlineStr"/>
       <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
@@ -990,28 +1014,28 @@
       <c r="M4" s="5" t="inlineStr"/>
       <c r="N4" s="5" t="inlineStr"/>
       <c r="O4" s="5" t="inlineStr"/>
-      <c r="P4" s="5" t="inlineStr"/>
-      <c r="Q4" s="4" t="inlineStr">
+      <c r="P4" s="6" t="inlineStr">
         <is>
           <t>CS202 LEC
 (CSE_2_B)
 Room: 101</t>
         </is>
       </c>
-      <c r="R4" s="4" t="inlineStr">
+      <c r="Q4" s="6" t="inlineStr">
         <is>
           <t>CS202 LEC
 (CSE_2_B)
 Room: 101</t>
         </is>
       </c>
-      <c r="S4" s="4" t="inlineStr">
+      <c r="R4" s="6" t="inlineStr">
         <is>
           <t>CS202 LEC
 (CSE_2_B)
 Room: 101</t>
         </is>
       </c>
+      <c r="S4" s="5" t="inlineStr"/>
       <c r="T4" s="5" t="inlineStr"/>
       <c r="U4" s="5" t="inlineStr"/>
     </row>
@@ -1026,34 +1050,10 @@
       <c r="D5" s="3" t="inlineStr"/>
       <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>CS202 LEC
-(CSE_2_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>CS202 LEC
-(CSE_2_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>CS202 LEC
-(CSE_2_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>CS202 LEC
-(CSE_2_B)
-Room: 101</t>
-        </is>
-      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
@@ -1293,28 +1293,28 @@
       <c r="L3" s="3" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="3" t="inlineStr"/>
-      <c r="O3" s="3" t="inlineStr"/>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>CS401 TUT
+(CSE_4_B)
+Room: 101</t>
+        </is>
+      </c>
       <c r="P3" s="4" t="inlineStr">
         <is>
-          <t>CS401 LEC
+          <t>CS401 TUT
 (CSE_4_B)
 Room: 101</t>
         </is>
       </c>
       <c r="Q3" s="4" t="inlineStr">
         <is>
-          <t>CS401 LEC
+          <t>CS401 TUT
 (CSE_4_B)
 Room: 101</t>
         </is>
       </c>
-      <c r="R3" s="4" t="inlineStr">
-        <is>
-          <t>CS401 LEC
-(CSE_4_B)
-Room: 101</t>
-        </is>
-      </c>
+      <c r="R3" s="3" t="inlineStr"/>
       <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="inlineStr"/>
@@ -1336,20 +1336,8 @@
       <c r="J4" s="5" t="inlineStr"/>
       <c r="K4" s="5" t="inlineStr"/>
       <c r="L4" s="5" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr">
-        <is>
-          <t>CS401 LEC
-(CSE_4_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>CS401 LEC
-(CSE_4_B)
-Room: 101</t>
-        </is>
-      </c>
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="inlineStr"/>
       <c r="O4" s="5" t="inlineStr"/>
       <c r="P4" s="5" t="inlineStr"/>
       <c r="Q4" s="5" t="inlineStr"/>
@@ -1367,10 +1355,34 @@
       <c r="B5" s="3" t="inlineStr"/>
       <c r="C5" s="3" t="inlineStr"/>
       <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr"/>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>CS401 LEC
+(CSE_4_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>CS401 LEC
+(CSE_4_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>CS401 LEC
+(CSE_4_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>CS401 LEC
+(CSE_4_B)
+Room: 101</t>
+        </is>
+      </c>
       <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="inlineStr"/>
@@ -1396,10 +1408,34 @@
       <c r="D6" s="5" t="inlineStr"/>
       <c r="E6" s="5" t="inlineStr"/>
       <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>CS401 LEC
+(CSE_4_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>CS401 LEC
+(CSE_4_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>CS401 LEC
+(CSE_4_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>CS401 LEC
+(CSE_4_B)
+Room: 101</t>
+        </is>
+      </c>
       <c r="K6" s="5" t="inlineStr"/>
       <c r="L6" s="5" t="inlineStr"/>
       <c r="M6" s="5" t="inlineStr"/>
@@ -1419,13 +1455,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr"/>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>CS401 TUT
-(CSE_4_B)
-Room: 101</t>
-        </is>
-      </c>
+      <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr"/>
@@ -1606,8 +1636,20 @@
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr"/>
-      <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr"/>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>CS402 LEC
+(CSE_4_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>CS402 LEC
+(CSE_4_B)
+Room: 101</t>
+        </is>
+      </c>
       <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr"/>
       <c r="G3" s="3" t="inlineStr"/>
@@ -1616,20 +1658,8 @@
       <c r="J3" s="3" t="inlineStr"/>
       <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>CS402 LEC
-(CSE_4_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>CS402 LEC
-(CSE_4_B)
-Room: 101</t>
-        </is>
-      </c>
+      <c r="M3" s="3" t="inlineStr"/>
+      <c r="N3" s="3" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr"/>
       <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" s="3" t="inlineStr"/>
@@ -1655,8 +1685,20 @@
       <c r="J4" s="5" t="inlineStr"/>
       <c r="K4" s="5" t="inlineStr"/>
       <c r="L4" s="5" t="inlineStr"/>
-      <c r="M4" s="5" t="inlineStr"/>
-      <c r="N4" s="5" t="inlineStr"/>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>CS402 LEC
+(CSE_4_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="N4" s="6" t="inlineStr">
+        <is>
+          <t>CS402 LEC
+(CSE_4_B)
+Room: 101</t>
+        </is>
+      </c>
       <c r="O4" s="5" t="inlineStr"/>
       <c r="P4" s="5" t="inlineStr"/>
       <c r="Q4" s="5" t="inlineStr"/>
@@ -1736,20 +1778,8 @@
       <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
-      <c r="M7" s="4" t="inlineStr">
-        <is>
-          <t>CS402 LEC
-(CSE_4_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="N7" s="4" t="inlineStr">
-        <is>
-          <t>CS402 LEC
-(CSE_4_B)
-Room: 101</t>
-        </is>
-      </c>
+      <c r="M7" s="3" t="inlineStr"/>
+      <c r="N7" s="3" t="inlineStr"/>
       <c r="O7" s="3" t="inlineStr"/>
       <c r="P7" s="3" t="inlineStr"/>
       <c r="Q7" s="3" t="inlineStr"/>
